--- a/artfynd/A 32038-2026 artfynd.xlsx
+++ b/artfynd/A 32038-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136700841</v>
       </c>
       <c r="B2" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>136700984</v>
       </c>
       <c r="B3" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>136701397</v>
       </c>
       <c r="B4" t="n">
-        <v>92538</v>
+        <v>92543</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>136700548</v>
       </c>
       <c r="B5" t="n">
-        <v>96664</v>
+        <v>96669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>136701384</v>
       </c>
       <c r="B6" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136700534</v>
       </c>
       <c r="B7" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136701400</v>
       </c>
       <c r="B8" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>136701431</v>
       </c>
       <c r="B9" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32038-2026 artfynd.xlsx
+++ b/artfynd/A 32038-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136700841</v>
       </c>
       <c r="B2" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>136700984</v>
       </c>
       <c r="B3" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>136701397</v>
       </c>
       <c r="B4" t="n">
-        <v>92543</v>
+        <v>92545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>136700548</v>
       </c>
       <c r="B5" t="n">
-        <v>96669</v>
+        <v>96671</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136700534</v>
       </c>
       <c r="B7" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136701400</v>
       </c>
       <c r="B8" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>136701431</v>
       </c>
       <c r="B9" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32038-2026 artfynd.xlsx
+++ b/artfynd/A 32038-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136700841</v>
       </c>
       <c r="B2" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>136700984</v>
       </c>
       <c r="B3" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>136701397</v>
       </c>
       <c r="B4" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>136700548</v>
       </c>
       <c r="B5" t="n">
-        <v>96671</v>
+        <v>96677</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>136701384</v>
       </c>
       <c r="B6" t="n">
-        <v>80602</v>
+        <v>80606</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136700534</v>
       </c>
       <c r="B7" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136701400</v>
       </c>
       <c r="B8" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>136701431</v>
       </c>
       <c r="B9" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32038-2026 artfynd.xlsx
+++ b/artfynd/A 32038-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136700841</v>
       </c>
       <c r="B2" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>136700984</v>
       </c>
       <c r="B3" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>136701397</v>
       </c>
       <c r="B4" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>136700548</v>
       </c>
       <c r="B5" t="n">
-        <v>96677</v>
+        <v>96679</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>136701384</v>
       </c>
       <c r="B6" t="n">
-        <v>80606</v>
+        <v>80608</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136700534</v>
       </c>
       <c r="B7" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136701400</v>
       </c>
       <c r="B8" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>136701431</v>
       </c>
       <c r="B9" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32038-2026 artfynd.xlsx
+++ b/artfynd/A 32038-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136700841</v>
       </c>
       <c r="B2" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>136700984</v>
       </c>
       <c r="B3" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>136701397</v>
       </c>
       <c r="B4" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>136700548</v>
       </c>
       <c r="B5" t="n">
-        <v>96679</v>
+        <v>96680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>136701384</v>
       </c>
       <c r="B6" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136700534</v>
       </c>
       <c r="B7" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136701400</v>
       </c>
       <c r="B8" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>136701431</v>
       </c>
       <c r="B9" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32038-2026 artfynd.xlsx
+++ b/artfynd/A 32038-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136700841</v>
       </c>
       <c r="B2" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>136700984</v>
       </c>
       <c r="B3" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>136701397</v>
       </c>
       <c r="B4" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>136700548</v>
       </c>
       <c r="B5" t="n">
-        <v>96680</v>
+        <v>96686</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136700534</v>
       </c>
       <c r="B7" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136701400</v>
       </c>
       <c r="B8" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>136701431</v>
       </c>
       <c r="B9" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32038-2026 artfynd.xlsx
+++ b/artfynd/A 32038-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136700841</v>
       </c>
       <c r="B2" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>136700984</v>
       </c>
       <c r="B3" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>136701397</v>
       </c>
       <c r="B4" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>136700548</v>
       </c>
       <c r="B5" t="n">
-        <v>96686</v>
+        <v>96690</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>136701384</v>
       </c>
       <c r="B6" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136700534</v>
       </c>
       <c r="B7" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136701400</v>
       </c>
       <c r="B8" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>136701431</v>
       </c>
       <c r="B9" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32038-2026 artfynd.xlsx
+++ b/artfynd/A 32038-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136700841</v>
       </c>
       <c r="B2" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>136700984</v>
       </c>
       <c r="B3" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>136700548</v>
       </c>
       <c r="B5" t="n">
-        <v>96690</v>
+        <v>96692</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136700534</v>
       </c>
       <c r="B7" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136701400</v>
       </c>
       <c r="B8" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>136701431</v>
       </c>
       <c r="B9" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32038-2026 artfynd.xlsx
+++ b/artfynd/A 32038-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136700841</v>
       </c>
       <c r="B2" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>136700984</v>
       </c>
       <c r="B3" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>136701397</v>
       </c>
       <c r="B4" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>136700548</v>
       </c>
       <c r="B5" t="n">
-        <v>96692</v>
+        <v>96694</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>136701384</v>
       </c>
       <c r="B6" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136700534</v>
       </c>
       <c r="B7" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136701400</v>
       </c>
       <c r="B8" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>136701431</v>
       </c>
       <c r="B9" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32038-2026 artfynd.xlsx
+++ b/artfynd/A 32038-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136700841</v>
       </c>
       <c r="B2" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>136700984</v>
       </c>
       <c r="B3" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>136701397</v>
       </c>
       <c r="B4" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>136700548</v>
       </c>
       <c r="B5" t="n">
-        <v>96694</v>
+        <v>96707</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>136701384</v>
       </c>
       <c r="B6" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136700534</v>
       </c>
       <c r="B7" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136701400</v>
       </c>
       <c r="B8" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>136701431</v>
       </c>
       <c r="B9" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32038-2026 artfynd.xlsx
+++ b/artfynd/A 32038-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136700841</v>
       </c>
       <c r="B2" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>136700984</v>
       </c>
       <c r="B3" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>136701397</v>
       </c>
       <c r="B4" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>136700548</v>
       </c>
       <c r="B5" t="n">
-        <v>96707</v>
+        <v>96709</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>136701384</v>
       </c>
       <c r="B6" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>136700534</v>
       </c>
       <c r="B7" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136701400</v>
       </c>
       <c r="B8" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>136701431</v>
       </c>
       <c r="B9" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32038-2026 artfynd.xlsx
+++ b/artfynd/A 32038-2026 artfynd.xlsx
@@ -710,11 +710,7 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med groddkorn</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -845,11 +841,7 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med groddkorn</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">

--- a/artfynd/A 32038-2026 artfynd.xlsx
+++ b/artfynd/A 32038-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136700841</v>
       </c>
       <c r="B2" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136700984</v>
       </c>
       <c r="B3" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>136701397</v>
       </c>
       <c r="B4" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>136700548</v>
       </c>
       <c r="B5" t="n">
-        <v>96709</v>
+        <v>96712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>136700534</v>
       </c>
       <c r="B7" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>136701400</v>
       </c>
       <c r="B8" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136701431</v>
       </c>
       <c r="B9" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32038-2026 artfynd.xlsx
+++ b/artfynd/A 32038-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136700841</v>
       </c>
       <c r="B2" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136700984</v>
       </c>
       <c r="B3" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>136701397</v>
       </c>
       <c r="B4" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>136700548</v>
       </c>
       <c r="B5" t="n">
-        <v>96712</v>
+        <v>96722</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>136701384</v>
       </c>
       <c r="B6" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>136700534</v>
       </c>
       <c r="B7" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>136701400</v>
       </c>
       <c r="B8" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>136701431</v>
       </c>
       <c r="B9" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
